--- a/out/employees_with_high_vaca_hours.xlsx
+++ b/out/employees_with_high_vaca_hours.xlsx
@@ -461,10 +461,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A2" t="n">
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -489,10 +487,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A3" t="n">
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -517,10 +513,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="A4" t="n">
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -545,10 +539,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="A5" t="n">
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -573,10 +565,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="A6" t="n">
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -601,10 +591,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A7" t="n">
+        <v>10</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -629,10 +617,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="A8" t="n">
+        <v>16</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -657,10 +643,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A9" t="n">
+        <v>18</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -685,10 +669,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="A10" t="n">
+        <v>19</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -713,10 +695,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="A11" t="n">
+        <v>20</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -741,10 +721,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="A12" t="n">
+        <v>21</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -769,10 +747,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="A13" t="n">
+        <v>22</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -797,10 +773,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="A14" t="n">
+        <v>23</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -825,10 +799,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="A15" t="n">
+        <v>25</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -853,10 +825,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="A16" t="n">
+        <v>28</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -881,10 +851,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="A17" t="n">
+        <v>29</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -909,10 +877,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="A18" t="n">
+        <v>30</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -937,10 +903,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="A19" t="n">
+        <v>37</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -965,10 +929,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="A20" t="n">
+        <v>38</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -993,10 +955,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="A21" t="n">
+        <v>39</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1021,10 +981,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="A22" t="n">
+        <v>40</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1049,10 +1007,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="A23" t="n">
+        <v>41</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1077,10 +1033,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="A24" t="n">
+        <v>42</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1105,10 +1059,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="A25" t="n">
+        <v>43</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1133,10 +1085,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+      <c r="A26" t="n">
+        <v>46</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1161,10 +1111,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="A27" t="n">
+        <v>52</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1189,10 +1137,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="A28" t="n">
+        <v>55</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1217,10 +1163,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="A29" t="n">
+        <v>57</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1245,10 +1189,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+      <c r="A30" t="n">
+        <v>58</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1273,10 +1215,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="A31" t="n">
+        <v>60</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1301,10 +1241,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="A32" t="n">
+        <v>64</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1329,10 +1267,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="A33" t="n">
+        <v>65</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1357,10 +1293,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="A34" t="n">
+        <v>66</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1385,10 +1319,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
+      <c r="A35" t="n">
+        <v>73</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1413,10 +1345,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="A36" t="n">
+        <v>74</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1441,10 +1371,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="A37" t="n">
+        <v>75</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1469,10 +1397,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="A38" t="n">
+        <v>76</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1497,10 +1423,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="A39" t="n">
+        <v>77</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1525,10 +1449,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="A40" t="n">
+        <v>78</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1553,10 +1475,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="A41" t="n">
+        <v>82</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1581,10 +1501,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="A42" t="n">
+        <v>83</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1609,10 +1527,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="A43" t="n">
+        <v>84</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1637,10 +1553,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
+      <c r="A44" t="n">
+        <v>91</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1665,10 +1579,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
+      <c r="A45" t="n">
+        <v>93</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1693,10 +1605,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
+      <c r="A46" t="n">
+        <v>94</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1721,10 +1631,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
+      <c r="A47" t="n">
+        <v>95</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1749,10 +1657,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
+      <c r="A48" t="n">
+        <v>96</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1777,10 +1683,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
+      <c r="A49" t="n">
+        <v>97</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1805,10 +1709,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="A50" t="n">
+        <v>100</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1833,10 +1735,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
+      <c r="A51" t="n">
+        <v>101</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -1861,10 +1761,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
+      <c r="A52" t="n">
+        <v>106</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -1889,10 +1787,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="A53" t="n">
+        <v>109</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -1917,10 +1813,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+      <c r="A54" t="n">
+        <v>111</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -1945,10 +1839,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
+      <c r="A55" t="n">
+        <v>112</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -1973,10 +1865,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+      <c r="A56" t="n">
+        <v>114</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2001,10 +1891,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
+      <c r="A57" t="n">
+        <v>118</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2029,10 +1917,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+      <c r="A58" t="n">
+        <v>119</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2057,10 +1943,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
+      <c r="A59" t="n">
+        <v>127</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2085,10 +1969,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
+      <c r="A60" t="n">
+        <v>128</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2113,10 +1995,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
+      <c r="A61" t="n">
+        <v>129</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2141,10 +2021,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
+      <c r="A62" t="n">
+        <v>130</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2169,10 +2047,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
+      <c r="A63" t="n">
+        <v>132</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2197,10 +2073,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
+      <c r="A64" t="n">
+        <v>133</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2225,10 +2099,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
+      <c r="A65" t="n">
+        <v>136</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2253,10 +2125,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
+      <c r="A66" t="n">
+        <v>142</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2281,10 +2151,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
+      <c r="A67" t="n">
+        <v>145</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2309,10 +2177,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
+      <c r="A68" t="n">
+        <v>146</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2337,10 +2203,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
+      <c r="A69" t="n">
+        <v>147</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2365,10 +2229,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
+      <c r="A70" t="n">
+        <v>148</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2393,10 +2255,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
+      <c r="A71" t="n">
+        <v>149</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2421,10 +2281,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+      <c r="A72" t="n">
+        <v>150</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -2449,10 +2307,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
+      <c r="A73" t="n">
+        <v>155</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2477,10 +2333,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
+      <c r="A74" t="n">
+        <v>156</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2505,10 +2359,8 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
+      <c r="A75" t="n">
+        <v>163</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2533,10 +2385,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
+      <c r="A76" t="n">
+        <v>165</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -2561,10 +2411,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
+      <c r="A77" t="n">
+        <v>167</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -2589,10 +2437,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
+      <c r="A78" t="n">
+        <v>168</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -2617,10 +2463,8 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
+      <c r="A79" t="n">
+        <v>169</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -2645,10 +2489,8 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
+      <c r="A80" t="n">
+        <v>172</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -2673,10 +2515,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
+      <c r="A81" t="n">
+        <v>173</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -2701,10 +2541,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
+      <c r="A82" t="n">
+        <v>174</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -2729,10 +2567,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
+      <c r="A83" t="n">
+        <v>180</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -2757,10 +2593,8 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
+      <c r="A84" t="n">
+        <v>181</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -2785,10 +2619,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
+      <c r="A85" t="n">
+        <v>182</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -2813,10 +2645,8 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
+      <c r="A86" t="n">
+        <v>183</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -2841,10 +2671,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
+      <c r="A87" t="n">
+        <v>184</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -2869,10 +2697,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
+      <c r="A88" t="n">
+        <v>191</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -2897,10 +2723,8 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
+      <c r="A89" t="n">
+        <v>192</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -2925,10 +2749,8 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
+      <c r="A90" t="n">
+        <v>196</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -2953,10 +2775,8 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
+      <c r="A91" t="n">
+        <v>197</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -2981,10 +2801,8 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
+      <c r="A92" t="n">
+        <v>198</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -3009,10 +2827,8 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
+      <c r="A93" t="n">
+        <v>199</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -3037,10 +2853,8 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
+      <c r="A94" t="n">
+        <v>201</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -3065,10 +2879,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
+      <c r="A95" t="n">
+        <v>202</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -3093,10 +2905,8 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
+      <c r="A96" t="n">
+        <v>203</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -3121,10 +2931,8 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
+      <c r="A97" t="n">
+        <v>204</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -3149,10 +2957,8 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
+      <c r="A98" t="n">
+        <v>205</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -3177,10 +2983,8 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
+      <c r="A99" t="n">
+        <v>209</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -3205,10 +3009,8 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
+      <c r="A100" t="n">
+        <v>210</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -3233,10 +3035,8 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
+      <c r="A101" t="n">
+        <v>217</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -3261,10 +3061,8 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
+      <c r="A102" t="n">
+        <v>219</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -3289,10 +3087,8 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
+      <c r="A103" t="n">
+        <v>220</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -3317,10 +3113,8 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
+      <c r="A104" t="n">
+        <v>221</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -3345,10 +3139,8 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
+      <c r="A105" t="n">
+        <v>226</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -3373,10 +3165,8 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
+      <c r="A106" t="n">
+        <v>227</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -3401,10 +3191,8 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
+      <c r="A107" t="n">
+        <v>228</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -3429,10 +3217,8 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
+      <c r="A108" t="n">
+        <v>236</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -3457,10 +3243,8 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
+      <c r="A109" t="n">
+        <v>238</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -3485,10 +3269,8 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="A110" t="n">
+        <v>240</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -3513,10 +3295,8 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
+      <c r="A111" t="n">
+        <v>244</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -3541,10 +3321,8 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
+      <c r="A112" t="n">
+        <v>245</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -3569,10 +3347,8 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
+      <c r="A113" t="n">
+        <v>250</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -3597,10 +3373,8 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
+      <c r="A114" t="n">
+        <v>253</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -3625,10 +3399,8 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
+      <c r="A115" t="n">
+        <v>254</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -3653,10 +3425,8 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
+      <c r="A116" t="n">
+        <v>255</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -3681,10 +3451,8 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
+      <c r="A117" t="n">
+        <v>256</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -3709,10 +3477,8 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
+      <c r="A118" t="n">
+        <v>257</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -3737,10 +3503,8 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
+      <c r="A119" t="n">
+        <v>258</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -3765,10 +3529,8 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
+      <c r="A120" t="n">
+        <v>259</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -3793,10 +3555,8 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
+      <c r="A121" t="n">
+        <v>262</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -3821,10 +3581,8 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
+      <c r="A122" t="n">
+        <v>274</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -3849,10 +3607,8 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
+      <c r="A123" t="n">
+        <v>275</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -3877,10 +3633,8 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
+      <c r="A124" t="n">
+        <v>276</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -3905,10 +3659,8 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
+      <c r="A125" t="n">
+        <v>277</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -3933,10 +3685,8 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
+      <c r="A126" t="n">
+        <v>280</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -3961,10 +3711,8 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
+      <c r="A127" t="n">
+        <v>282</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -3989,10 +3737,8 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
+      <c r="A128" t="n">
+        <v>286</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -4017,10 +3763,8 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
+      <c r="A129" t="n">
+        <v>287</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -4045,10 +3789,8 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
+      <c r="A130" t="n">
+        <v>289</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -4073,10 +3815,8 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
+      <c r="A131" t="n">
+        <v>290</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -4101,10 +3841,8 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
+      <c r="A132" t="n">
+        <v>291</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -4129,10 +3867,8 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
+      <c r="A133" t="n">
+        <v>292</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -4157,10 +3893,8 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
+      <c r="A134" t="n">
+        <v>294</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -4185,10 +3919,8 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
+      <c r="A135" t="n">
+        <v>299</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -4213,10 +3945,8 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
+      <c r="A136" t="n">
+        <v>300</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -4241,10 +3971,8 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
+      <c r="A137" t="n">
+        <v>304</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -4269,10 +3997,8 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
+      <c r="A138" t="n">
+        <v>306</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -4297,10 +4023,8 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
+      <c r="A139" t="n">
+        <v>307</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -4325,10 +4049,8 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
+      <c r="A140" t="n">
+        <v>309</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -4353,10 +4075,8 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
+      <c r="A141" t="n">
+        <v>312</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -4381,10 +4101,8 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
+      <c r="A142" t="n">
+        <v>313</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -4409,10 +4127,8 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
+      <c r="A143" t="n">
+        <v>316</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -4437,10 +4153,8 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
+      <c r="A144" t="n">
+        <v>317</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -4465,10 +4179,8 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
+      <c r="A145" t="n">
+        <v>318</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -4493,10 +4205,8 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
+      <c r="A146" t="n">
+        <v>322</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -4521,10 +4231,8 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
+      <c r="A147" t="n">
+        <v>325</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -4549,10 +4257,8 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
+      <c r="A148" t="n">
+        <v>326</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -4577,10 +4283,8 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="A149" t="n">
+        <v>328</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -4605,10 +4309,8 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
+      <c r="A150" t="n">
+        <v>330</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -4633,10 +4335,8 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
+      <c r="A151" t="n">
+        <v>331</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -4661,10 +4361,8 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
+      <c r="A152" t="n">
+        <v>334</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -4689,10 +4387,8 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
+      <c r="A153" t="n">
+        <v>335</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -4717,10 +4413,8 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>344</t>
-        </is>
+      <c r="A154" t="n">
+        <v>344</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -4745,10 +4439,8 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
+      <c r="A155" t="n">
+        <v>345</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -4773,10 +4465,8 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
+      <c r="A156" t="n">
+        <v>347</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -4801,10 +4491,8 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
+      <c r="A157" t="n">
+        <v>348</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -4829,10 +4517,8 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
+      <c r="A158" t="n">
+        <v>352</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -4857,10 +4543,8 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
+      <c r="A159" t="n">
+        <v>354</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -4885,10 +4569,8 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
+      <c r="A160" t="n">
+        <v>358</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -4913,10 +4595,8 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
+      <c r="A161" t="n">
+        <v>360</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -4941,10 +4621,8 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
+      <c r="A162" t="n">
+        <v>362</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -4969,10 +4647,8 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
+      <c r="A163" t="n">
+        <v>363</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -4997,10 +4673,8 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>365</t>
-        </is>
+      <c r="A164" t="n">
+        <v>365</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -5025,10 +4699,8 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
+      <c r="A165" t="n">
+        <v>366</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -5053,10 +4725,8 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
+      <c r="A166" t="n">
+        <v>367</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -5081,10 +4751,8 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
+      <c r="A167" t="n">
+        <v>370</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -5109,10 +4777,8 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
+      <c r="A168" t="n">
+        <v>371</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -5137,10 +4803,8 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
+      <c r="A169" t="n">
+        <v>376</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -5165,10 +4829,8 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
+      <c r="A170" t="n">
+        <v>379</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -5193,10 +4855,8 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
+      <c r="A171" t="n">
+        <v>381</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -5221,10 +4881,8 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
+      <c r="A172" t="n">
+        <v>382</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -5249,10 +4907,8 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
+      <c r="A173" t="n">
+        <v>384</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -5277,10 +4933,8 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
+      <c r="A174" t="n">
+        <v>385</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -5305,10 +4959,8 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
+      <c r="A175" t="n">
+        <v>388</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -5333,10 +4985,8 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
+      <c r="A176" t="n">
+        <v>394</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -5361,10 +5011,8 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
+      <c r="A177" t="n">
+        <v>398</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -5389,10 +5037,8 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
+      <c r="A178" t="n">
+        <v>400</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -5417,10 +5063,8 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
+      <c r="A179" t="n">
+        <v>403</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -5445,10 +5089,8 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>406</t>
-        </is>
+      <c r="A180" t="n">
+        <v>406</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -5473,10 +5115,8 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
+      <c r="A181" t="n">
+        <v>412</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -5501,10 +5141,8 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>415</t>
-        </is>
+      <c r="A182" t="n">
+        <v>415</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -5529,10 +5167,8 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
+      <c r="A183" t="n">
+        <v>416</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -5557,10 +5193,8 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
+      <c r="A184" t="n">
+        <v>417</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -5585,10 +5219,8 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
+      <c r="A185" t="n">
+        <v>418</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -5613,10 +5245,8 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
+      <c r="A186" t="n">
+        <v>419</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -5641,10 +5271,8 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
+      <c r="A187" t="n">
+        <v>420</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -5669,10 +5297,8 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>426</t>
-        </is>
+      <c r="A188" t="n">
+        <v>426</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -5697,10 +5323,8 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
+      <c r="A189" t="n">
+        <v>430</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -5725,10 +5349,8 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
+      <c r="A190" t="n">
+        <v>431</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -5753,10 +5375,8 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
+      <c r="A191" t="n">
+        <v>433</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -5781,10 +5401,8 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
+      <c r="A192" t="n">
+        <v>434</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -5809,10 +5427,8 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
+      <c r="A193" t="n">
+        <v>438</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -5837,10 +5453,8 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>439</t>
-        </is>
+      <c r="A194" t="n">
+        <v>439</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -5865,10 +5479,8 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
+      <c r="A195" t="n">
+        <v>442</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -5893,10 +5505,8 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
+      <c r="A196" t="n">
+        <v>443</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -5921,10 +5531,8 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
+      <c r="A197" t="n">
+        <v>444</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -5949,10 +5557,8 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>451</t>
-        </is>
+      <c r="A198" t="n">
+        <v>451</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -5977,10 +5583,8 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
+      <c r="A199" t="n">
+        <v>452</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -6005,10 +5609,8 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>453</t>
-        </is>
+      <c r="A200" t="n">
+        <v>453</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -6033,10 +5635,8 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>454</t>
-        </is>
+      <c r="A201" t="n">
+        <v>454</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -6061,10 +5661,8 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
+      <c r="A202" t="n">
+        <v>456</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -6089,10 +5687,8 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>460</t>
-        </is>
+      <c r="A203" t="n">
+        <v>460</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -6117,10 +5713,8 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
+      <c r="A204" t="n">
+        <v>461</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -6145,10 +5739,8 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>462</t>
-        </is>
+      <c r="A205" t="n">
+        <v>462</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -6173,10 +5765,8 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
+      <c r="A206" t="n">
+        <v>466</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -6201,10 +5791,8 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
+      <c r="A207" t="n">
+        <v>470</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -6229,10 +5817,8 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
+      <c r="A208" t="n">
+        <v>471</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -6257,10 +5843,8 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
+      <c r="A209" t="n">
+        <v>473</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -6285,10 +5869,8 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
+      <c r="A210" t="n">
+        <v>474</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -6313,10 +5895,8 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
+      <c r="A211" t="n">
+        <v>479</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -6341,10 +5921,8 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
+      <c r="A212" t="n">
+        <v>487</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -6369,10 +5947,8 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
+      <c r="A213" t="n">
+        <v>488</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -6397,10 +5973,8 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
+      <c r="A214" t="n">
+        <v>492</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -6425,10 +5999,8 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
+      <c r="A215" t="n">
+        <v>493</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -6453,10 +6025,8 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
+      <c r="A216" t="n">
+        <v>496</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -6481,10 +6051,8 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
+      <c r="A217" t="n">
+        <v>497</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -6509,10 +6077,8 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>498</t>
-        </is>
+      <c r="A218" t="n">
+        <v>498</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -6537,10 +6103,8 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
+      <c r="A219" t="n">
+        <v>505</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -6565,10 +6129,8 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
+      <c r="A220" t="n">
+        <v>506</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -6593,10 +6155,8 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
+      <c r="A221" t="n">
+        <v>507</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -6621,10 +6181,8 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>514</t>
-        </is>
+      <c r="A222" t="n">
+        <v>514</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -6649,10 +6207,8 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
+      <c r="A223" t="n">
+        <v>515</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -6677,10 +6233,8 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>516</t>
-        </is>
+      <c r="A224" t="n">
+        <v>516</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -6705,10 +6259,8 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
+      <c r="A225" t="n">
+        <v>523</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -6733,10 +6285,8 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
+      <c r="A226" t="n">
+        <v>526</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -6761,10 +6311,8 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>527</t>
-        </is>
+      <c r="A227" t="n">
+        <v>527</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -6789,10 +6337,8 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>528</t>
-        </is>
+      <c r="A228" t="n">
+        <v>528</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -6817,10 +6363,8 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>533</t>
-        </is>
+      <c r="A229" t="n">
+        <v>533</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -6845,10 +6389,8 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>534</t>
-        </is>
+      <c r="A230" t="n">
+        <v>534</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -6873,10 +6415,8 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>541</t>
-        </is>
+      <c r="A231" t="n">
+        <v>541</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -6901,10 +6441,8 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>542</t>
-        </is>
+      <c r="A232" t="n">
+        <v>542</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -6929,10 +6467,8 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
+      <c r="A233" t="n">
+        <v>543</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -6957,10 +6493,8 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
+      <c r="A234" t="n">
+        <v>545</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -6985,10 +6519,8 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>546</t>
-        </is>
+      <c r="A235" t="n">
+        <v>546</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -7013,10 +6545,8 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
+      <c r="A236" t="n">
+        <v>551</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -7041,10 +6571,8 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>559</t>
-        </is>
+      <c r="A237" t="n">
+        <v>559</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -7069,10 +6597,8 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
+      <c r="A238" t="n">
+        <v>560</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -7097,10 +6623,8 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
+      <c r="A239" t="n">
+        <v>561</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -7125,10 +6649,8 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>563</t>
-        </is>
+      <c r="A240" t="n">
+        <v>563</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -7153,10 +6675,8 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>565</t>
-        </is>
+      <c r="A241" t="n">
+        <v>565</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -7181,10 +6701,8 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
+      <c r="A242" t="n">
+        <v>568</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -7209,10 +6727,8 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>569</t>
-        </is>
+      <c r="A243" t="n">
+        <v>569</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -7237,10 +6753,8 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>574</t>
-        </is>
+      <c r="A244" t="n">
+        <v>574</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -7265,10 +6779,8 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
+      <c r="A245" t="n">
+        <v>578</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -7293,10 +6805,8 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
+      <c r="A246" t="n">
+        <v>579</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -7321,10 +6831,8 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>582</t>
-        </is>
+      <c r="A247" t="n">
+        <v>582</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -7349,10 +6857,8 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
+      <c r="A248" t="n">
+        <v>586</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -7377,10 +6883,8 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
+      <c r="A249" t="n">
+        <v>587</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -7405,10 +6909,8 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
+      <c r="A250" t="n">
+        <v>588</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -7433,10 +6935,8 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
+      <c r="A251" t="n">
+        <v>592</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -7461,10 +6961,8 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
+      <c r="A252" t="n">
+        <v>596</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -7489,10 +6987,8 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
+      <c r="A253" t="n">
+        <v>597</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -7517,10 +7013,8 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
+      <c r="A254" t="n">
+        <v>598</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -7545,10 +7039,8 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
+      <c r="A255" t="n">
+        <v>601</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -7573,10 +7065,8 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
+      <c r="A256" t="n">
+        <v>604</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -7601,10 +7091,8 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
+      <c r="A257" t="n">
+        <v>609</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -7629,10 +7117,8 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
+      <c r="A258" t="n">
+        <v>610</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -7657,10 +7143,8 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
+      <c r="A259" t="n">
+        <v>617</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -7685,10 +7169,8 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
+      <c r="A260" t="n">
+        <v>621</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -7713,10 +7195,8 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
+      <c r="A261" t="n">
+        <v>622</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -7741,10 +7221,8 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>623</t>
-        </is>
+      <c r="A262" t="n">
+        <v>623</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -7769,10 +7247,8 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
+      <c r="A263" t="n">
+        <v>624</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -7797,10 +7273,8 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
+      <c r="A264" t="n">
+        <v>631</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -7825,10 +7299,8 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
+      <c r="A265" t="n">
+        <v>635</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -7853,10 +7325,8 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
+      <c r="A266" t="n">
+        <v>641</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -7881,10 +7351,8 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
+      <c r="A267" t="n">
+        <v>643</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -7909,10 +7377,8 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
+      <c r="A268" t="n">
+        <v>644</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -7937,10 +7403,8 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
+      <c r="A269" t="n">
+        <v>645</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
@@ -7965,10 +7429,8 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
+      <c r="A270" t="n">
+        <v>647</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -7993,10 +7455,8 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
+      <c r="A271" t="n">
+        <v>659</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -8021,10 +7481,8 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>660</t>
-        </is>
+      <c r="A272" t="n">
+        <v>660</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -8049,10 +7507,8 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
+      <c r="A273" t="n">
+        <v>668</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -8077,10 +7533,8 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
+      <c r="A274" t="n">
+        <v>669</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -8105,10 +7559,8 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
+      <c r="A275" t="n">
+        <v>670</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -8133,10 +7585,8 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>671</t>
-        </is>
+      <c r="A276" t="n">
+        <v>671</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -8161,10 +7611,8 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
+      <c r="A277" t="n">
+        <v>672</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
@@ -8189,10 +7637,8 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
+      <c r="A278" t="n">
+        <v>673</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -8217,10 +7663,8 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
+      <c r="A279" t="n">
+        <v>677</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
@@ -8245,10 +7689,8 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
+      <c r="A280" t="n">
+        <v>678</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
@@ -8273,10 +7715,8 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
+      <c r="A281" t="n">
+        <v>683</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
@@ -8301,10 +7741,8 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
+      <c r="A282" t="n">
+        <v>689</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
@@ -8329,10 +7767,8 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
+      <c r="A283" t="n">
+        <v>692</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
@@ -8357,10 +7793,8 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
+      <c r="A284" t="n">
+        <v>694</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
@@ -8385,10 +7819,8 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
+      <c r="A285" t="n">
+        <v>696</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
@@ -8413,10 +7845,8 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
+      <c r="A286" t="n">
+        <v>697</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
@@ -8441,10 +7871,8 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
+      <c r="A287" t="n">
+        <v>701</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
@@ -8469,10 +7897,8 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>29485</t>
-        </is>
+      <c r="A288" t="n">
+        <v>29485</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
@@ -8497,10 +7923,8 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>29490</t>
-        </is>
+      <c r="A289" t="n">
+        <v>29490</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
@@ -8525,10 +7949,8 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>29492</t>
-        </is>
+      <c r="A290" t="n">
+        <v>29492</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
@@ -8553,10 +7975,8 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>29494</t>
-        </is>
+      <c r="A291" t="n">
+        <v>29494</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
@@ -8581,10 +8001,8 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>29499</t>
-        </is>
+      <c r="A292" t="n">
+        <v>29499</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
@@ -8609,10 +8027,8 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>29503</t>
-        </is>
+      <c r="A293" t="n">
+        <v>29503</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
@@ -8637,10 +8053,8 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>29505</t>
-        </is>
+      <c r="A294" t="n">
+        <v>29505</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
@@ -8665,10 +8079,8 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>29506</t>
-        </is>
+      <c r="A295" t="n">
+        <v>29506</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
@@ -8693,10 +8105,8 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>29510</t>
-        </is>
+      <c r="A296" t="n">
+        <v>29510</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
@@ -8721,10 +8131,8 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>29511</t>
-        </is>
+      <c r="A297" t="n">
+        <v>29511</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
@@ -8749,10 +8157,8 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>29517</t>
-        </is>
+      <c r="A298" t="n">
+        <v>29517</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
@@ -8777,10 +8183,8 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>29521</t>
-        </is>
+      <c r="A299" t="n">
+        <v>29521</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
@@ -8805,10 +8209,8 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>29523</t>
-        </is>
+      <c r="A300" t="n">
+        <v>29523</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
@@ -8833,10 +8235,8 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>29525</t>
-        </is>
+      <c r="A301" t="n">
+        <v>29525</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
@@ -8861,10 +8261,8 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>29527</t>
-        </is>
+      <c r="A302" t="n">
+        <v>29527</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
@@ -8889,10 +8287,8 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>29530</t>
-        </is>
+      <c r="A303" t="n">
+        <v>29530</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
@@ -8917,10 +8313,8 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>29532</t>
-        </is>
+      <c r="A304" t="n">
+        <v>29532</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
@@ -8945,10 +8339,8 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>29535</t>
-        </is>
+      <c r="A305" t="n">
+        <v>29535</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
@@ -8973,10 +8365,8 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>29536</t>
-        </is>
+      <c r="A306" t="n">
+        <v>29536</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
@@ -9001,10 +8391,8 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>29539</t>
-        </is>
+      <c r="A307" t="n">
+        <v>29539</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
@@ -9029,10 +8417,8 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>29541</t>
-        </is>
+      <c r="A308" t="n">
+        <v>29541</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
@@ -9057,10 +8443,8 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>29544</t>
-        </is>
+      <c r="A309" t="n">
+        <v>29544</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
@@ -9085,10 +8469,8 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>29545</t>
-        </is>
+      <c r="A310" t="n">
+        <v>29545</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
@@ -9113,10 +8495,8 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>29546</t>
-        </is>
+      <c r="A311" t="n">
+        <v>29546</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
@@ -9141,10 +8521,8 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>29548</t>
-        </is>
+      <c r="A312" t="n">
+        <v>29548</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
@@ -9169,10 +8547,8 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>29553</t>
-        </is>
+      <c r="A313" t="n">
+        <v>29553</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
@@ -9197,10 +8573,8 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>29558</t>
-        </is>
+      <c r="A314" t="n">
+        <v>29558</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
@@ -9225,10 +8599,8 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>29560</t>
-        </is>
+      <c r="A315" t="n">
+        <v>29560</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
@@ -9253,10 +8625,8 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>29562</t>
-        </is>
+      <c r="A316" t="n">
+        <v>29562</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
@@ -9281,10 +8651,8 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>29567</t>
-        </is>
+      <c r="A317" t="n">
+        <v>29567</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
@@ -9309,10 +8677,8 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>29568</t>
-        </is>
+      <c r="A318" t="n">
+        <v>29568</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
@@ -9337,10 +8703,8 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>29569</t>
-        </is>
+      <c r="A319" t="n">
+        <v>29569</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
@@ -9365,10 +8729,8 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>29570</t>
-        </is>
+      <c r="A320" t="n">
+        <v>29570</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
@@ -9393,10 +8755,8 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>29571</t>
-        </is>
+      <c r="A321" t="n">
+        <v>29571</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
@@ -9421,10 +8781,8 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>29573</t>
-        </is>
+      <c r="A322" t="n">
+        <v>29573</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
@@ -9449,10 +8807,8 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>29574</t>
-        </is>
+      <c r="A323" t="n">
+        <v>29574</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
@@ -9477,10 +8833,8 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>29577</t>
-        </is>
+      <c r="A324" t="n">
+        <v>29577</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
@@ -9505,10 +8859,8 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>29580</t>
-        </is>
+      <c r="A325" t="n">
+        <v>29580</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
@@ -9533,10 +8885,8 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>29582</t>
-        </is>
+      <c r="A326" t="n">
+        <v>29582</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
@@ -9561,10 +8911,8 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>29583</t>
-        </is>
+      <c r="A327" t="n">
+        <v>29583</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
@@ -9589,10 +8937,8 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>29585</t>
-        </is>
+      <c r="A328" t="n">
+        <v>29585</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
@@ -9617,10 +8963,8 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>29587</t>
-        </is>
+      <c r="A329" t="n">
+        <v>29587</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
@@ -9645,10 +8989,8 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>29588</t>
-        </is>
+      <c r="A330" t="n">
+        <v>29588</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
@@ -9673,10 +9015,8 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>29591</t>
-        </is>
+      <c r="A331" t="n">
+        <v>29591</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
@@ -9701,10 +9041,8 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>29593</t>
-        </is>
+      <c r="A332" t="n">
+        <v>29593</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
@@ -9729,10 +9067,8 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>29600</t>
-        </is>
+      <c r="A333" t="n">
+        <v>29600</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
@@ -9757,10 +9093,8 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>29601</t>
-        </is>
+      <c r="A334" t="n">
+        <v>29601</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
@@ -9785,10 +9119,8 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>29603</t>
-        </is>
+      <c r="A335" t="n">
+        <v>29603</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
@@ -9813,10 +9145,8 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>29605</t>
-        </is>
+      <c r="A336" t="n">
+        <v>29605</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
@@ -9841,10 +9171,8 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>29606</t>
-        </is>
+      <c r="A337" t="n">
+        <v>29606</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
@@ -9869,10 +9197,8 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>29611</t>
-        </is>
+      <c r="A338" t="n">
+        <v>29611</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
@@ -9897,10 +9223,8 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>29614</t>
-        </is>
+      <c r="A339" t="n">
+        <v>29614</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
@@ -9925,10 +9249,8 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>29615</t>
-        </is>
+      <c r="A340" t="n">
+        <v>29615</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
@@ -9953,10 +9275,8 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>29616</t>
-        </is>
+      <c r="A341" t="n">
+        <v>29616</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
@@ -9981,10 +9301,8 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>29620</t>
-        </is>
+      <c r="A342" t="n">
+        <v>29620</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
@@ -10009,10 +9327,8 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>29625</t>
-        </is>
+      <c r="A343" t="n">
+        <v>29625</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
@@ -10037,10 +9353,8 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>29629</t>
-        </is>
+      <c r="A344" t="n">
+        <v>29629</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
@@ -10065,10 +9379,8 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>29631</t>
-        </is>
+      <c r="A345" t="n">
+        <v>29631</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
@@ -10093,10 +9405,8 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>29632</t>
-        </is>
+      <c r="A346" t="n">
+        <v>29632</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
@@ -10121,10 +9431,8 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>29638</t>
-        </is>
+      <c r="A347" t="n">
+        <v>29638</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
@@ -10149,10 +9457,8 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>29641</t>
-        </is>
+      <c r="A348" t="n">
+        <v>29641</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
@@ -10177,10 +9483,8 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>29644</t>
-        </is>
+      <c r="A349" t="n">
+        <v>29644</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
@@ -10205,10 +9509,8 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>29646</t>
-        </is>
+      <c r="A350" t="n">
+        <v>29646</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
@@ -10233,10 +9535,8 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>29653</t>
-        </is>
+      <c r="A351" t="n">
+        <v>29653</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
@@ -10261,10 +9561,8 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
+      <c r="A352" t="n">
+        <v>29655</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
@@ -10289,10 +9587,8 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>29659</t>
-        </is>
+      <c r="A353" t="n">
+        <v>29659</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
@@ -10317,10 +9613,8 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>29660</t>
-        </is>
+      <c r="A354" t="n">
+        <v>29660</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
@@ -10345,10 +9639,8 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>29662</t>
-        </is>
+      <c r="A355" t="n">
+        <v>29662</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
@@ -10373,10 +9665,8 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>29663</t>
-        </is>
+      <c r="A356" t="n">
+        <v>29663</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
@@ -10401,10 +9691,8 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>29666</t>
-        </is>
+      <c r="A357" t="n">
+        <v>29666</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
@@ -10429,10 +9717,8 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>29668</t>
-        </is>
+      <c r="A358" t="n">
+        <v>29668</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
@@ -10457,10 +9743,8 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>29673</t>
-        </is>
+      <c r="A359" t="n">
+        <v>29673</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
@@ -10485,10 +9769,8 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>29674</t>
-        </is>
+      <c r="A360" t="n">
+        <v>29674</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
@@ -10513,10 +9795,8 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>29677</t>
-        </is>
+      <c r="A361" t="n">
+        <v>29677</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
@@ -10541,10 +9821,8 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>29680</t>
-        </is>
+      <c r="A362" t="n">
+        <v>29680</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
@@ -10569,10 +9847,8 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>29682</t>
-        </is>
+      <c r="A363" t="n">
+        <v>29682</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
@@ -10597,10 +9873,8 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>29683</t>
-        </is>
+      <c r="A364" t="n">
+        <v>29683</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
@@ -10625,10 +9899,8 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>29684</t>
-        </is>
+      <c r="A365" t="n">
+        <v>29684</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
@@ -10653,10 +9925,8 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>29688</t>
-        </is>
+      <c r="A366" t="n">
+        <v>29688</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
@@ -10681,10 +9951,8 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>29690</t>
-        </is>
+      <c r="A367" t="n">
+        <v>29690</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
@@ -10709,10 +9977,8 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>29698</t>
-        </is>
+      <c r="A368" t="n">
+        <v>29698</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
@@ -10737,10 +10003,8 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>29699</t>
-        </is>
+      <c r="A369" t="n">
+        <v>29699</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
@@ -10765,10 +10029,8 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>29702</t>
-        </is>
+      <c r="A370" t="n">
+        <v>29702</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
@@ -10793,10 +10055,8 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>29703</t>
-        </is>
+      <c r="A371" t="n">
+        <v>29703</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
@@ -10821,10 +10081,8 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>29710</t>
-        </is>
+      <c r="A372" t="n">
+        <v>29710</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
@@ -10849,10 +10107,8 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>29711</t>
-        </is>
+      <c r="A373" t="n">
+        <v>29711</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
@@ -10877,10 +10133,8 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>29713</t>
-        </is>
+      <c r="A374" t="n">
+        <v>29713</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
@@ -10905,10 +10159,8 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>29714</t>
-        </is>
+      <c r="A375" t="n">
+        <v>29714</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
@@ -10933,10 +10185,8 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>29719</t>
-        </is>
+      <c r="A376" t="n">
+        <v>29719</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
@@ -10961,10 +10211,8 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>29727</t>
-        </is>
+      <c r="A377" t="n">
+        <v>29727</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
@@ -10989,10 +10237,8 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>29728</t>
-        </is>
+      <c r="A378" t="n">
+        <v>29728</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
@@ -11017,10 +10263,8 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
+      <c r="A379" t="n">
+        <v>29730</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
@@ -11045,10 +10289,8 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>29733</t>
-        </is>
+      <c r="A380" t="n">
+        <v>29733</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
@@ -11073,10 +10315,8 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>29734</t>
-        </is>
+      <c r="A381" t="n">
+        <v>29734</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
@@ -11101,10 +10341,8 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>29736</t>
-        </is>
+      <c r="A382" t="n">
+        <v>29736</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
@@ -11129,10 +10367,8 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>29737</t>
-        </is>
+      <c r="A383" t="n">
+        <v>29737</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
@@ -11157,10 +10393,8 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>29739</t>
-        </is>
+      <c r="A384" t="n">
+        <v>29739</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
@@ -11185,10 +10419,8 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>29741</t>
-        </is>
+      <c r="A385" t="n">
+        <v>29741</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
@@ -11213,10 +10445,8 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>29742</t>
-        </is>
+      <c r="A386" t="n">
+        <v>29742</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
@@ -11241,10 +10471,8 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>29743</t>
-        </is>
+      <c r="A387" t="n">
+        <v>29743</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
@@ -11269,10 +10497,8 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>29744</t>
-        </is>
+      <c r="A388" t="n">
+        <v>29744</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
@@ -11297,10 +10523,8 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>29747</t>
-        </is>
+      <c r="A389" t="n">
+        <v>29747</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
@@ -11325,10 +10549,8 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>29748</t>
-        </is>
+      <c r="A390" t="n">
+        <v>29748</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
@@ -11353,10 +10575,8 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>29750</t>
-        </is>
+      <c r="A391" t="n">
+        <v>29750</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
@@ -11381,10 +10601,8 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>29753</t>
-        </is>
+      <c r="A392" t="n">
+        <v>29753</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
@@ -11409,10 +10627,8 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>29757</t>
-        </is>
+      <c r="A393" t="n">
+        <v>29757</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
@@ -11437,10 +10653,8 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>29758</t>
-        </is>
+      <c r="A394" t="n">
+        <v>29758</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
@@ -11465,10 +10679,8 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>29763</t>
-        </is>
+      <c r="A395" t="n">
+        <v>29763</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
@@ -11493,10 +10705,8 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>29764</t>
-        </is>
+      <c r="A396" t="n">
+        <v>29764</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
@@ -11521,10 +10731,8 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>29765</t>
-        </is>
+      <c r="A397" t="n">
+        <v>29765</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
@@ -11549,10 +10757,8 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>29766</t>
-        </is>
+      <c r="A398" t="n">
+        <v>29766</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
@@ -11577,10 +10783,8 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>29768</t>
-        </is>
+      <c r="A399" t="n">
+        <v>29768</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
@@ -11605,10 +10809,8 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>29769</t>
-        </is>
+      <c r="A400" t="n">
+        <v>29769</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
@@ -11633,10 +10835,8 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>29770</t>
-        </is>
+      <c r="A401" t="n">
+        <v>29770</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
@@ -11661,10 +10861,8 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>29771</t>
-        </is>
+      <c r="A402" t="n">
+        <v>29771</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
@@ -11689,10 +10887,8 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>29772</t>
-        </is>
+      <c r="A403" t="n">
+        <v>29772</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
@@ -11717,10 +10913,8 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>29778</t>
-        </is>
+      <c r="A404" t="n">
+        <v>29778</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
@@ -11745,10 +10939,8 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>29780</t>
-        </is>
+      <c r="A405" t="n">
+        <v>29780</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
@@ -11773,10 +10965,8 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>29782</t>
-        </is>
+      <c r="A406" t="n">
+        <v>29782</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
@@ -11801,10 +10991,8 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>29783</t>
-        </is>
+      <c r="A407" t="n">
+        <v>29783</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
@@ -11829,10 +11017,8 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>29787</t>
-        </is>
+      <c r="A408" t="n">
+        <v>29787</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
@@ -11857,10 +11043,8 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>29788</t>
-        </is>
+      <c r="A409" t="n">
+        <v>29788</v>
       </c>
       <c r="B409" t="inlineStr">
         <is>
@@ -11885,10 +11069,8 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>29789</t>
-        </is>
+      <c r="A410" t="n">
+        <v>29789</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
@@ -11913,10 +11095,8 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>29792</t>
-        </is>
+      <c r="A411" t="n">
+        <v>29792</v>
       </c>
       <c r="B411" t="inlineStr">
         <is>
@@ -11941,10 +11121,8 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>29794</t>
-        </is>
+      <c r="A412" t="n">
+        <v>29794</v>
       </c>
       <c r="B412" t="inlineStr">
         <is>
@@ -11969,10 +11147,8 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>29796</t>
-        </is>
+      <c r="A413" t="n">
+        <v>29796</v>
       </c>
       <c r="B413" t="inlineStr">
         <is>
@@ -11997,10 +11173,8 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>29799</t>
-        </is>
+      <c r="A414" t="n">
+        <v>29799</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
@@ -12025,10 +11199,8 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>29805</t>
-        </is>
+      <c r="A415" t="n">
+        <v>29805</v>
       </c>
       <c r="B415" t="inlineStr">
         <is>
@@ -12053,10 +11225,8 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>29806</t>
-        </is>
+      <c r="A416" t="n">
+        <v>29806</v>
       </c>
       <c r="B416" t="inlineStr">
         <is>
@@ -12081,10 +11251,8 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>29807</t>
-        </is>
+      <c r="A417" t="n">
+        <v>29807</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
@@ -12109,10 +11277,8 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>29809</t>
-        </is>
+      <c r="A418" t="n">
+        <v>29809</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
@@ -12137,10 +11303,8 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>29810</t>
-        </is>
+      <c r="A419" t="n">
+        <v>29810</v>
       </c>
       <c r="B419" t="inlineStr">
         <is>
@@ -12165,10 +11329,8 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>29813</t>
-        </is>
+      <c r="A420" t="n">
+        <v>29813</v>
       </c>
       <c r="B420" t="inlineStr">
         <is>
@@ -12193,10 +11355,8 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>29815</t>
-        </is>
+      <c r="A421" t="n">
+        <v>29815</v>
       </c>
       <c r="B421" t="inlineStr">
         <is>
@@ -12221,10 +11381,8 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>29818</t>
-        </is>
+      <c r="A422" t="n">
+        <v>29818</v>
       </c>
       <c r="B422" t="inlineStr">
         <is>
@@ -12249,10 +11407,8 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>29819</t>
-        </is>
+      <c r="A423" t="n">
+        <v>29819</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
@@ -12277,10 +11433,8 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>29822</t>
-        </is>
+      <c r="A424" t="n">
+        <v>29822</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
@@ -12305,10 +11459,8 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>29824</t>
-        </is>
+      <c r="A425" t="n">
+        <v>29824</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
@@ -12333,10 +11485,8 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>29826</t>
-        </is>
+      <c r="A426" t="n">
+        <v>29826</v>
       </c>
       <c r="B426" t="inlineStr">
         <is>
@@ -12361,10 +11511,8 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>29827</t>
-        </is>
+      <c r="A427" t="n">
+        <v>29827</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
@@ -12389,10 +11537,8 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>29831</t>
-        </is>
+      <c r="A428" t="n">
+        <v>29831</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
@@ -12417,10 +11563,8 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>29834</t>
-        </is>
+      <c r="A429" t="n">
+        <v>29834</v>
       </c>
       <c r="B429" t="inlineStr">
         <is>
@@ -12445,10 +11589,8 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>29835</t>
-        </is>
+      <c r="A430" t="n">
+        <v>29835</v>
       </c>
       <c r="B430" t="inlineStr">
         <is>
@@ -12473,10 +11615,8 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>29840</t>
-        </is>
+      <c r="A431" t="n">
+        <v>29840</v>
       </c>
       <c r="B431" t="inlineStr">
         <is>
@@ -12501,10 +11641,8 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>29848</t>
-        </is>
+      <c r="A432" t="n">
+        <v>29848</v>
       </c>
       <c r="B432" t="inlineStr">
         <is>
@@ -12529,10 +11667,8 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>29852</t>
-        </is>
+      <c r="A433" t="n">
+        <v>29852</v>
       </c>
       <c r="B433" t="inlineStr">
         <is>
@@ -12557,10 +11693,8 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>29853</t>
-        </is>
+      <c r="A434" t="n">
+        <v>29853</v>
       </c>
       <c r="B434" t="inlineStr">
         <is>
@@ -12585,10 +11719,8 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>29854</t>
-        </is>
+      <c r="A435" t="n">
+        <v>29854</v>
       </c>
       <c r="B435" t="inlineStr">
         <is>
@@ -12613,10 +11745,8 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>29855</t>
-        </is>
+      <c r="A436" t="n">
+        <v>29855</v>
       </c>
       <c r="B436" t="inlineStr">
         <is>
@@ -12641,10 +11771,8 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>29857</t>
-        </is>
+      <c r="A437" t="n">
+        <v>29857</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
@@ -12669,10 +11797,8 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>29859</t>
-        </is>
+      <c r="A438" t="n">
+        <v>29859</v>
       </c>
       <c r="B438" t="inlineStr">
         <is>
@@ -12697,10 +11823,8 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>29860</t>
-        </is>
+      <c r="A439" t="n">
+        <v>29860</v>
       </c>
       <c r="B439" t="inlineStr">
         <is>
@@ -12725,10 +11849,8 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>29861</t>
-        </is>
+      <c r="A440" t="n">
+        <v>29861</v>
       </c>
       <c r="B440" t="inlineStr">
         <is>
@@ -12753,10 +11875,8 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>29863</t>
-        </is>
+      <c r="A441" t="n">
+        <v>29863</v>
       </c>
       <c r="B441" t="inlineStr">
         <is>
@@ -12781,10 +11901,8 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>29864</t>
-        </is>
+      <c r="A442" t="n">
+        <v>29864</v>
       </c>
       <c r="B442" t="inlineStr">
         <is>
@@ -12809,10 +11927,8 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>29865</t>
-        </is>
+      <c r="A443" t="n">
+        <v>29865</v>
       </c>
       <c r="B443" t="inlineStr">
         <is>
@@ -12837,10 +11953,8 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>29867</t>
-        </is>
+      <c r="A444" t="n">
+        <v>29867</v>
       </c>
       <c r="B444" t="inlineStr">
         <is>
@@ -12865,10 +11979,8 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>29868</t>
-        </is>
+      <c r="A445" t="n">
+        <v>29868</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
@@ -12893,10 +12005,8 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>29870</t>
-        </is>
+      <c r="A446" t="n">
+        <v>29870</v>
       </c>
       <c r="B446" t="inlineStr">
         <is>
@@ -12921,10 +12031,8 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>29872</t>
-        </is>
+      <c r="A447" t="n">
+        <v>29872</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
@@ -12949,10 +12057,8 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>29873</t>
-        </is>
+      <c r="A448" t="n">
+        <v>29873</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
@@ -12977,10 +12083,8 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>29876</t>
-        </is>
+      <c r="A449" t="n">
+        <v>29876</v>
       </c>
       <c r="B449" t="inlineStr">
         <is>
@@ -13005,10 +12109,8 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>29877</t>
-        </is>
+      <c r="A450" t="n">
+        <v>29877</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
@@ -13033,10 +12135,8 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>29879</t>
-        </is>
+      <c r="A451" t="n">
+        <v>29879</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
@@ -13061,10 +12161,8 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>29881</t>
-        </is>
+      <c r="A452" t="n">
+        <v>29881</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
@@ -13089,10 +12187,8 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>29883</t>
-        </is>
+      <c r="A453" t="n">
+        <v>29883</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
@@ -13117,10 +12213,8 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>29884</t>
-        </is>
+      <c r="A454" t="n">
+        <v>29884</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
@@ -13145,10 +12239,8 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>29885</t>
-        </is>
+      <c r="A455" t="n">
+        <v>29885</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
@@ -13173,10 +12265,8 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>29889</t>
-        </is>
+      <c r="A456" t="n">
+        <v>29889</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
@@ -13201,10 +12291,8 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>29890</t>
-        </is>
+      <c r="A457" t="n">
+        <v>29890</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
@@ -13229,10 +12317,8 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>29893</t>
-        </is>
+      <c r="A458" t="n">
+        <v>29893</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
@@ -13257,10 +12343,8 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>29895</t>
-        </is>
+      <c r="A459" t="n">
+        <v>29895</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
@@ -13285,10 +12369,8 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>29900</t>
-        </is>
+      <c r="A460" t="n">
+        <v>29900</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
@@ -13313,10 +12395,8 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>29901</t>
-        </is>
+      <c r="A461" t="n">
+        <v>29901</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
@@ -13341,10 +12421,8 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>29905</t>
-        </is>
+      <c r="A462" t="n">
+        <v>29905</v>
       </c>
       <c r="B462" t="inlineStr">
         <is>
@@ -13369,10 +12447,8 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>29907</t>
-        </is>
+      <c r="A463" t="n">
+        <v>29907</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
@@ -13397,10 +12473,8 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>29908</t>
-        </is>
+      <c r="A464" t="n">
+        <v>29908</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
@@ -13425,10 +12499,8 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>29910</t>
-        </is>
+      <c r="A465" t="n">
+        <v>29910</v>
       </c>
       <c r="B465" t="inlineStr">
         <is>
@@ -13453,10 +12525,8 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>29911</t>
-        </is>
+      <c r="A466" t="n">
+        <v>29911</v>
       </c>
       <c r="B466" t="inlineStr">
         <is>
@@ -13481,10 +12551,8 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>29913</t>
-        </is>
+      <c r="A467" t="n">
+        <v>29913</v>
       </c>
       <c r="B467" t="inlineStr">
         <is>
@@ -13509,10 +12577,8 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>29914</t>
-        </is>
+      <c r="A468" t="n">
+        <v>29914</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
@@ -13537,10 +12603,8 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>29915</t>
-        </is>
+      <c r="A469" t="n">
+        <v>29915</v>
       </c>
       <c r="B469" t="inlineStr">
         <is>
@@ -13565,10 +12629,8 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>29918</t>
-        </is>
+      <c r="A470" t="n">
+        <v>29918</v>
       </c>
       <c r="B470" t="inlineStr">
         <is>
@@ -13593,10 +12655,8 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>29919</t>
-        </is>
+      <c r="A471" t="n">
+        <v>29919</v>
       </c>
       <c r="B471" t="inlineStr">
         <is>
@@ -13621,10 +12681,8 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>29920</t>
-        </is>
+      <c r="A472" t="n">
+        <v>29920</v>
       </c>
       <c r="B472" t="inlineStr">
         <is>
@@ -13649,10 +12707,8 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>29921</t>
-        </is>
+      <c r="A473" t="n">
+        <v>29921</v>
       </c>
       <c r="B473" t="inlineStr">
         <is>
@@ -13677,10 +12733,8 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>29924</t>
-        </is>
+      <c r="A474" t="n">
+        <v>29924</v>
       </c>
       <c r="B474" t="inlineStr">
         <is>
@@ -13705,10 +12759,8 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>29926</t>
-        </is>
+      <c r="A475" t="n">
+        <v>29926</v>
       </c>
       <c r="B475" t="inlineStr">
         <is>
@@ -13733,10 +12785,8 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>29928</t>
-        </is>
+      <c r="A476" t="n">
+        <v>29928</v>
       </c>
       <c r="B476" t="inlineStr">
         <is>
@@ -13761,10 +12811,8 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>29930</t>
-        </is>
+      <c r="A477" t="n">
+        <v>29930</v>
       </c>
       <c r="B477" t="inlineStr">
         <is>
@@ -13789,10 +12837,8 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>29932</t>
-        </is>
+      <c r="A478" t="n">
+        <v>29932</v>
       </c>
       <c r="B478" t="inlineStr">
         <is>
@@ -13817,10 +12863,8 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>29935</t>
-        </is>
+      <c r="A479" t="n">
+        <v>29935</v>
       </c>
       <c r="B479" t="inlineStr">
         <is>
@@ -13845,10 +12889,8 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>29936</t>
-        </is>
+      <c r="A480" t="n">
+        <v>29936</v>
       </c>
       <c r="B480" t="inlineStr">
         <is>
@@ -13873,10 +12915,8 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>29937</t>
-        </is>
+      <c r="A481" t="n">
+        <v>29937</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
@@ -13901,10 +12941,8 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>29938</t>
-        </is>
+      <c r="A482" t="n">
+        <v>29938</v>
       </c>
       <c r="B482" t="inlineStr">
         <is>
@@ -13929,10 +12967,8 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>29939</t>
-        </is>
+      <c r="A483" t="n">
+        <v>29939</v>
       </c>
       <c r="B483" t="inlineStr">
         <is>
@@ -13957,10 +12993,8 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>29941</t>
-        </is>
+      <c r="A484" t="n">
+        <v>29941</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
@@ -13985,10 +13019,8 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>29943</t>
-        </is>
+      <c r="A485" t="n">
+        <v>29943</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
@@ -14013,10 +13045,8 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>29944</t>
-        </is>
+      <c r="A486" t="n">
+        <v>29944</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
@@ -14041,10 +13071,8 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>29948</t>
-        </is>
+      <c r="A487" t="n">
+        <v>29948</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
@@ -14069,10 +13097,8 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>29949</t>
-        </is>
+      <c r="A488" t="n">
+        <v>29949</v>
       </c>
       <c r="B488" t="inlineStr">
         <is>
@@ -14097,10 +13123,8 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>29950</t>
-        </is>
+      <c r="A489" t="n">
+        <v>29950</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
@@ -14125,10 +13149,8 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>29952</t>
-        </is>
+      <c r="A490" t="n">
+        <v>29952</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
@@ -14153,10 +13175,8 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>29953</t>
-        </is>
+      <c r="A491" t="n">
+        <v>29953</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
@@ -14181,10 +13201,8 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>29955</t>
-        </is>
+      <c r="A492" t="n">
+        <v>29955</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
@@ -14209,10 +13227,8 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>29956</t>
-        </is>
+      <c r="A493" t="n">
+        <v>29956</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
@@ -14237,10 +13253,8 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>29957</t>
-        </is>
+      <c r="A494" t="n">
+        <v>29957</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
@@ -14265,10 +13279,8 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>29967</t>
-        </is>
+      <c r="A495" t="n">
+        <v>29967</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
@@ -14293,10 +13305,8 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>29973</t>
-        </is>
+      <c r="A496" t="n">
+        <v>29973</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
@@ -14321,10 +13331,8 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>29974</t>
-        </is>
+      <c r="A497" t="n">
+        <v>29974</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
@@ -14349,10 +13357,8 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>29975</t>
-        </is>
+      <c r="A498" t="n">
+        <v>29975</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
@@ -14377,10 +13383,8 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>29978</t>
-        </is>
+      <c r="A499" t="n">
+        <v>29978</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
@@ -14405,10 +13409,8 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>29980</t>
-        </is>
+      <c r="A500" t="n">
+        <v>29980</v>
       </c>
       <c r="B500" t="inlineStr">
         <is>
@@ -14433,10 +13435,8 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>29982</t>
-        </is>
+      <c r="A501" t="n">
+        <v>29982</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
@@ -14461,10 +13461,8 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>29985</t>
-        </is>
+      <c r="A502" t="n">
+        <v>29985</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
@@ -14489,10 +13487,8 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>29987</t>
-        </is>
+      <c r="A503" t="n">
+        <v>29987</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
@@ -14517,10 +13513,8 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>29988</t>
-        </is>
+      <c r="A504" t="n">
+        <v>29988</v>
       </c>
       <c r="B504" t="inlineStr">
         <is>
@@ -14545,10 +13539,8 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>29990</t>
-        </is>
+      <c r="A505" t="n">
+        <v>29990</v>
       </c>
       <c r="B505" t="inlineStr">
         <is>
@@ -14573,10 +13565,8 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>29991</t>
-        </is>
+      <c r="A506" t="n">
+        <v>29991</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
@@ -14601,10 +13591,8 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>29992</t>
-        </is>
+      <c r="A507" t="n">
+        <v>29992</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
@@ -14629,10 +13617,8 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>29994</t>
-        </is>
+      <c r="A508" t="n">
+        <v>29994</v>
       </c>
       <c r="B508" t="inlineStr">
         <is>
@@ -14657,10 +13643,8 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>29998</t>
-        </is>
+      <c r="A509" t="n">
+        <v>29998</v>
       </c>
       <c r="B509" t="inlineStr">
         <is>
@@ -14685,10 +13669,8 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
+      <c r="A510" t="n">
+        <v>30000</v>
       </c>
       <c r="B510" t="inlineStr">
         <is>
@@ -14713,10 +13695,8 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>30003</t>
-        </is>
+      <c r="A511" t="n">
+        <v>30003</v>
       </c>
       <c r="B511" t="inlineStr">
         <is>
@@ -14741,10 +13721,8 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>30005</t>
-        </is>
+      <c r="A512" t="n">
+        <v>30005</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
@@ -14769,10 +13747,8 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>30007</t>
-        </is>
+      <c r="A513" t="n">
+        <v>30007</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
@@ -14797,10 +13773,8 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>30008</t>
-        </is>
+      <c r="A514" t="n">
+        <v>30008</v>
       </c>
       <c r="B514" t="inlineStr">
         <is>
@@ -14825,10 +13799,8 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>30010</t>
-        </is>
+      <c r="A515" t="n">
+        <v>30010</v>
       </c>
       <c r="B515" t="inlineStr">
         <is>
@@ -14853,10 +13825,8 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>30018</t>
-        </is>
+      <c r="A516" t="n">
+        <v>30018</v>
       </c>
       <c r="B516" t="inlineStr">
         <is>
@@ -14881,10 +13851,8 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>30019</t>
-        </is>
+      <c r="A517" t="n">
+        <v>30019</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
@@ -14909,10 +13877,8 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>30021</t>
-        </is>
+      <c r="A518" t="n">
+        <v>30021</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
@@ -14937,10 +13903,8 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>30024</t>
-        </is>
+      <c r="A519" t="n">
+        <v>30024</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
@@ -14965,10 +13929,8 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>30025</t>
-        </is>
+      <c r="A520" t="n">
+        <v>30025</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
@@ -14993,10 +13955,8 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>30028</t>
-        </is>
+      <c r="A521" t="n">
+        <v>30028</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
@@ -15021,10 +13981,8 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>30029</t>
-        </is>
+      <c r="A522" t="n">
+        <v>30029</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
@@ -15049,10 +14007,8 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>30032</t>
-        </is>
+      <c r="A523" t="n">
+        <v>30032</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
@@ -15077,10 +14033,8 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>30033</t>
-        </is>
+      <c r="A524" t="n">
+        <v>30033</v>
       </c>
       <c r="B524" t="inlineStr">
         <is>
@@ -15105,10 +14059,8 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>30034</t>
-        </is>
+      <c r="A525" t="n">
+        <v>30034</v>
       </c>
       <c r="B525" t="inlineStr">
         <is>
@@ -15133,10 +14085,8 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>30035</t>
-        </is>
+      <c r="A526" t="n">
+        <v>30035</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
@@ -15161,10 +14111,8 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>30037</t>
-        </is>
+      <c r="A527" t="n">
+        <v>30037</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
@@ -15189,10 +14137,8 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>30039</t>
-        </is>
+      <c r="A528" t="n">
+        <v>30039</v>
       </c>
       <c r="B528" t="inlineStr">
         <is>
@@ -15217,10 +14163,8 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>30042</t>
-        </is>
+      <c r="A529" t="n">
+        <v>30042</v>
       </c>
       <c r="B529" t="inlineStr">
         <is>
@@ -15245,10 +14189,8 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>30046</t>
-        </is>
+      <c r="A530" t="n">
+        <v>30046</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
@@ -15273,10 +14215,8 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>30047</t>
-        </is>
+      <c r="A531" t="n">
+        <v>30047</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
@@ -15301,10 +14241,8 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>30048</t>
-        </is>
+      <c r="A532" t="n">
+        <v>30048</v>
       </c>
       <c r="B532" t="inlineStr">
         <is>
@@ -15329,10 +14267,8 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>30050</t>
-        </is>
+      <c r="A533" t="n">
+        <v>30050</v>
       </c>
       <c r="B533" t="inlineStr">
         <is>
@@ -15357,10 +14293,8 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" t="inlineStr">
-        <is>
-          <t>30051</t>
-        </is>
+      <c r="A534" t="n">
+        <v>30051</v>
       </c>
       <c r="B534" t="inlineStr">
         <is>
@@ -15385,10 +14319,8 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>30053</t>
-        </is>
+      <c r="A535" t="n">
+        <v>30053</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
@@ -15413,10 +14345,8 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
-          <t>30055</t>
-        </is>
+      <c r="A536" t="n">
+        <v>30055</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
@@ -15441,10 +14371,8 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>30058</t>
-        </is>
+      <c r="A537" t="n">
+        <v>30058</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
@@ -15469,10 +14397,8 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>30061</t>
-        </is>
+      <c r="A538" t="n">
+        <v>30061</v>
       </c>
       <c r="B538" t="inlineStr">
         <is>
@@ -15497,10 +14423,8 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>30064</t>
-        </is>
+      <c r="A539" t="n">
+        <v>30064</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
@@ -15525,10 +14449,8 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" t="inlineStr">
-        <is>
-          <t>30067</t>
-        </is>
+      <c r="A540" t="n">
+        <v>30067</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
@@ -15553,10 +14475,8 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" t="inlineStr">
-        <is>
-          <t>30071</t>
-        </is>
+      <c r="A541" t="n">
+        <v>30071</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
@@ -15581,10 +14501,8 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
-          <t>30072</t>
-        </is>
+      <c r="A542" t="n">
+        <v>30072</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
@@ -15609,10 +14527,8 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>30076</t>
-        </is>
+      <c r="A543" t="n">
+        <v>30076</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
@@ -15637,10 +14553,8 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>30083</t>
-        </is>
+      <c r="A544" t="n">
+        <v>30083</v>
       </c>
       <c r="B544" t="inlineStr">
         <is>
@@ -15665,10 +14579,8 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>30087</t>
-        </is>
+      <c r="A545" t="n">
+        <v>30087</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
@@ -15693,10 +14605,8 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" t="inlineStr">
-        <is>
-          <t>30090</t>
-        </is>
+      <c r="A546" t="n">
+        <v>30090</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
@@ -15721,10 +14631,8 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" t="inlineStr">
-        <is>
-          <t>30093</t>
-        </is>
+      <c r="A547" t="n">
+        <v>30093</v>
       </c>
       <c r="B547" t="inlineStr">
         <is>
@@ -15749,10 +14657,8 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" t="inlineStr">
-        <is>
-          <t>30094</t>
-        </is>
+      <c r="A548" t="n">
+        <v>30094</v>
       </c>
       <c r="B548" t="inlineStr">
         <is>
@@ -15777,10 +14683,8 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" t="inlineStr">
-        <is>
-          <t>30102</t>
-        </is>
+      <c r="A549" t="n">
+        <v>30102</v>
       </c>
       <c r="B549" t="inlineStr">
         <is>
@@ -15805,10 +14709,8 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" t="inlineStr">
-        <is>
-          <t>30105</t>
-        </is>
+      <c r="A550" t="n">
+        <v>30105</v>
       </c>
       <c r="B550" t="inlineStr">
         <is>
@@ -15833,10 +14735,8 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" t="inlineStr">
-        <is>
-          <t>30106</t>
-        </is>
+      <c r="A551" t="n">
+        <v>30106</v>
       </c>
       <c r="B551" t="inlineStr">
         <is>
@@ -15861,10 +14761,8 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" t="inlineStr">
-        <is>
-          <t>30107</t>
-        </is>
+      <c r="A552" t="n">
+        <v>30107</v>
       </c>
       <c r="B552" t="inlineStr">
         <is>
@@ -15889,10 +14787,8 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" t="inlineStr">
-        <is>
-          <t>30110</t>
-        </is>
+      <c r="A553" t="n">
+        <v>30110</v>
       </c>
       <c r="B553" t="inlineStr">
         <is>
@@ -15917,10 +14813,8 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" t="inlineStr">
-        <is>
-          <t>30112</t>
-        </is>
+      <c r="A554" t="n">
+        <v>30112</v>
       </c>
       <c r="B554" t="inlineStr">
         <is>
@@ -15945,10 +14839,8 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" t="inlineStr">
-        <is>
-          <t>30113</t>
-        </is>
+      <c r="A555" t="n">
+        <v>30113</v>
       </c>
       <c r="B555" t="inlineStr">
         <is>
